--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487395_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487395_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.5326</v>
+        <v>4.0931</v>
       </c>
       <c r="E2" t="n">
-        <v>3.7078</v>
+        <v>4.3218</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.1752</v>
+        <v>-0.2287</v>
       </c>
       <c r="G2" t="n">
         <v>-1.2996</v>
@@ -610,13 +610,13 @@
         <v>3.1336</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.5814</v>
+        <v>-0.0209</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.8205</v>
+        <v>-0.2064</v>
       </c>
       <c r="U2" t="n">
-        <v>0.239</v>
+        <v>0.1856</v>
       </c>
       <c r="V2" t="n">
         <v>3.2593</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>R. BLANCO CARBALLO</t>
+          <t>D. LASTRA GONZALEZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,22 +643,22 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1348</v>
+        <v>-0.0182</v>
       </c>
       <c r="E3" t="n">
-        <v>0.6837</v>
+        <v>0.2655</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.5489000000000001</v>
+        <v>-0.2837</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.2746</v>
+        <v>-0.4787</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.0473</v>
+        <v>-0.3879</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.2273</v>
+        <v>-0.09080000000000001</v>
       </c>
       <c r="J3" t="n">
         <v>0.0608</v>
@@ -670,46 +670,46 @@
         <v>0.0404</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.3354</v>
+        <v>-0.5396</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.0677</v>
+        <v>-0.4083</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.2677</v>
+        <v>-0.1313</v>
       </c>
       <c r="P3" t="n">
-        <v>0.1958</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>0.1958</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>0.2135</v>
+        <v>0.1276</v>
       </c>
       <c r="T3" t="n">
-        <v>0.6228</v>
+        <v>0.2047</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.4093</v>
+        <v>-0.077</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>0.3329</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>0.3329</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>D. LASTRA GONZALEZ</t>
+          <t>R. BLANCO CARBALLO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,22 +721,22 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.2228</v>
+        <v>-0.2746</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0608</v>
+        <v>0.2743</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.2837</v>
+        <v>-0.5489000000000001</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.4787</v>
+        <v>-0.2746</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.3879</v>
+        <v>-0.0473</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.09080000000000001</v>
+        <v>-0.2273</v>
       </c>
       <c r="J4" t="n">
         <v>0.0608</v>
@@ -748,46 +748,46 @@
         <v>0.0404</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.5396</v>
+        <v>-0.3354</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.4083</v>
+        <v>-0.0677</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.1313</v>
+        <v>-0.2677</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>0.1958</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>0.1958</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.077</v>
+        <v>-0.1958</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>0.2135</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.077</v>
+        <v>-0.4093</v>
       </c>
       <c r="V4" t="n">
-        <v>0.3329</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>0.3329</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>I. LUCENTE</t>
+          <t>P. NJIE</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.7079</v>
+        <v>-0.7769</v>
       </c>
       <c r="E5" t="n">
-        <v>2.757</v>
+        <v>-0.8697</v>
       </c>
       <c r="F5" t="n">
-        <v>-3.4649</v>
+        <v>0.09279999999999999</v>
       </c>
       <c r="G5" t="n">
-        <v>-2.3205</v>
+        <v>-0.795</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.5782</v>
+        <v>-0.1687</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.7423</v>
+        <v>-0.6262</v>
       </c>
       <c r="J5" t="n">
-        <v>2.1303</v>
+        <v>0.1425</v>
       </c>
       <c r="K5" t="n">
-        <v>0.1904</v>
+        <v>0.1021</v>
       </c>
       <c r="L5" t="n">
-        <v>1.9399</v>
+        <v>0.0404</v>
       </c>
       <c r="M5" t="n">
-        <v>-4.4508</v>
+        <v>-0.9375</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.7686</v>
+        <v>-0.2708</v>
       </c>
       <c r="O5" t="n">
-        <v>-2.6822</v>
+        <v>-0.6667</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.3917</v>
+        <v>-0.1958</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.9585</v>
+        <v>-0.9792</v>
       </c>
       <c r="R5" t="n">
-        <v>1.5668</v>
+        <v>0.7834</v>
       </c>
       <c r="S5" t="n">
-        <v>2.3372</v>
+        <v>0.2139</v>
       </c>
       <c r="T5" t="n">
-        <v>1.7015</v>
+        <v>-0.0329</v>
       </c>
       <c r="U5" t="n">
-        <v>0.6358</v>
+        <v>0.2469</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.3329</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>0.8837</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.2166</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>P. NJIE</t>
+          <t>I. LUCENTE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.9608</v>
+        <v>-1.7939</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.1338</v>
+        <v>1.9383</v>
       </c>
       <c r="F6" t="n">
-        <v>0.173</v>
+        <v>-3.7322</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.795</v>
+        <v>-2.3205</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.1687</v>
+        <v>-1.5782</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.6262</v>
+        <v>-0.7423</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1425</v>
+        <v>2.1303</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1021</v>
+        <v>0.1904</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0404</v>
+        <v>1.9399</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.9375</v>
+        <v>-4.4508</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.2708</v>
+        <v>-1.7686</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.6667</v>
+        <v>-2.6822</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.1958</v>
+        <v>-0.3917</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.9792</v>
+        <v>-1.9585</v>
       </c>
       <c r="R6" t="n">
-        <v>0.7834</v>
+        <v>1.5668</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0301</v>
+        <v>1.2513</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.297</v>
+        <v>0.8828</v>
       </c>
       <c r="U6" t="n">
-        <v>0.3271</v>
+        <v>0.3685</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>-0.3329</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>0.8837</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-1.2166</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.3418</v>
+        <v>-2.3321</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.8491</v>
+        <v>-1.278</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.4927</v>
+        <v>-1.0541</v>
       </c>
       <c r="G7" t="n">
         <v>-4.8533</v>
@@ -1000,13 +1000,13 @@
         <v>3.5253</v>
       </c>
       <c r="S7" t="n">
-        <v>0.8491</v>
+        <v>0.8588</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.6487000000000001</v>
+        <v>-0.0776</v>
       </c>
       <c r="U7" t="n">
-        <v>1.4978</v>
+        <v>0.9365</v>
       </c>
       <c r="V7" t="n">
         <v>-0.8837</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>C. FERNANDEZ ALVAREZ</t>
+          <t>A. BARRIOS UREÑA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,64 +1033,64 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-3.0538</v>
+        <v>-3.1883</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.9913999999999999</v>
+        <v>-0.08400000000000001</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.0624</v>
+        <v>-3.1043</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.4597</v>
+        <v>-1.5802</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.6922</v>
+        <v>1.5365</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.7675</v>
+        <v>-3.1168</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.7826</v>
+        <v>3.2581</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.9443</v>
+        <v>3.1677</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1617</v>
+        <v>0.0905</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.677</v>
+        <v>-4.8384</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.7479</v>
+        <v>-1.6311</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.9292</v>
+        <v>-3.2073</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>-0.9792</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.9792</v>
+        <v>-3.917</v>
       </c>
       <c r="R8" t="n">
-        <v>0.9792</v>
+        <v>2.9377</v>
       </c>
       <c r="S8" t="n">
-        <v>0.6225000000000001</v>
+        <v>-0.2958</v>
       </c>
       <c r="T8" t="n">
-        <v>0.7705</v>
+        <v>-0.3088</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.148</v>
+        <v>0.0129</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.2166</v>
+        <v>-0.3329</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>0.8837</v>
       </c>
       <c r="X8" t="n">
         <v>-1.2166</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. PACHECO MARTINEZ</t>
+          <t>S. SHARASHIDZE</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.3364</v>
+        <v>-3.2698</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.8944</v>
+        <v>-3.2035</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.442</v>
+        <v>-0.0663</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.9095</v>
+        <v>-3.816</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.6622</v>
+        <v>-3.0985</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.2473</v>
+        <v>-0.7175</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.0387</v>
+        <v>-0.9348</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.1195</v>
+        <v>-2.0809</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0808</v>
+        <v>1.1461</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.8708</v>
+        <v>-2.8812</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.5427</v>
+        <v>-1.0176</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.3281</v>
+        <v>-1.8635</v>
       </c>
       <c r="P9" t="n">
-        <v>0.5875</v>
+        <v>-1.5668</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.9792</v>
+        <v>-3.917</v>
       </c>
       <c r="R9" t="n">
-        <v>1.5668</v>
+        <v>2.3502</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.1309</v>
+        <v>0.5634</v>
       </c>
       <c r="T9" t="n">
-        <v>0.1235</v>
+        <v>0.4317</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2544</v>
+        <v>0.1317</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.8837</v>
+        <v>1.5495</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.2166</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.8837</v>
+        <v>0.3329</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>S. SHARASHIDZE</t>
+          <t>C. FERNANDEZ ALVAREZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.8454</v>
+        <v>-3.454</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.6722</v>
+        <v>-1.6054</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.1732</v>
+        <v>-1.8485</v>
       </c>
       <c r="G10" t="n">
-        <v>-3.816</v>
+        <v>-2.4597</v>
       </c>
       <c r="H10" t="n">
-        <v>-3.0985</v>
+        <v>-1.6922</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.7175</v>
+        <v>-0.7675</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.9348</v>
+        <v>-0.7826</v>
       </c>
       <c r="K10" t="n">
-        <v>-2.0809</v>
+        <v>-0.9443</v>
       </c>
       <c r="L10" t="n">
-        <v>1.1461</v>
+        <v>0.1617</v>
       </c>
       <c r="M10" t="n">
-        <v>-2.8812</v>
+        <v>-1.677</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.0176</v>
+        <v>-0.7479</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.8635</v>
+        <v>-0.9292</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.5668</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>-3.917</v>
+        <v>-0.9792</v>
       </c>
       <c r="R10" t="n">
-        <v>2.3502</v>
+        <v>0.9792</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.0122</v>
+        <v>0.2223</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.0371</v>
+        <v>0.1564</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0248</v>
+        <v>0.0659</v>
       </c>
       <c r="V10" t="n">
-        <v>1.5495</v>
+        <v>-1.2166</v>
       </c>
       <c r="W10" t="n">
-        <v>1.2166</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0.3329</v>
+        <v>-1.2166</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A. BARRIOS UREÑA</t>
+          <t>A. PACHECO MARTINEZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.2756</v>
+        <v>-3.5098</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.0644</v>
+        <v>-2.2014</v>
       </c>
       <c r="F11" t="n">
-        <v>-3.2112</v>
+        <v>-1.3084</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.5802</v>
+        <v>-2.9095</v>
       </c>
       <c r="H11" t="n">
-        <v>1.5365</v>
+        <v>-1.6622</v>
       </c>
       <c r="I11" t="n">
-        <v>-3.1168</v>
+        <v>-1.2473</v>
       </c>
       <c r="J11" t="n">
-        <v>3.2581</v>
+        <v>-1.0387</v>
       </c>
       <c r="K11" t="n">
-        <v>3.1677</v>
+        <v>-1.1195</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0905</v>
+        <v>0.0808</v>
       </c>
       <c r="M11" t="n">
-        <v>-4.8384</v>
+        <v>-1.8708</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.6311</v>
+        <v>-0.5427</v>
       </c>
       <c r="O11" t="n">
-        <v>-3.2073</v>
+        <v>-1.3281</v>
       </c>
       <c r="P11" t="n">
+        <v>0.5875</v>
+      </c>
+      <c r="Q11" t="n">
         <v>-0.9792</v>
       </c>
-      <c r="Q11" t="n">
-        <v>-3.917</v>
-      </c>
       <c r="R11" t="n">
-        <v>2.9377</v>
+        <v>1.5668</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.3832</v>
+        <v>-0.3042</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.2892</v>
+        <v>-0.1835</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.094</v>
+        <v>-0.1207</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.3329</v>
+        <v>-0.8837</v>
       </c>
       <c r="W11" t="n">
-        <v>0.8837</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.2166</v>
+        <v>-0.8837</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.5605</v>
+        <v>-5.8165</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.1696</v>
+        <v>-3.8266</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.3909</v>
+        <v>-1.99</v>
       </c>
       <c r="G12" t="n">
         <v>-7.2741</v>
@@ -1390,13 +1390,13 @@
         <v>2.546</v>
       </c>
       <c r="S12" t="n">
-        <v>1.126</v>
+        <v>0.87</v>
       </c>
       <c r="T12" t="n">
-        <v>1.2857</v>
+        <v>0.6287</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.1597</v>
+        <v>0.2413</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-20.6376</v>
+        <v>-20.341</v>
       </c>
       <c r="E13" t="n">
-        <v>-6.5656</v>
+        <v>-6.268700000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>-14.0721</v>
+        <v>-14.0723</v>
       </c>
       <c r="G13" t="n">
         <v>-28.0612</v>
@@ -1441,13 +1441,13 @@
         <v>-15.4318</v>
       </c>
       <c r="J13" t="n">
-        <v>2.151400000000001</v>
+        <v>2.151399999999999</v>
       </c>
       <c r="K13" t="n">
         <v>-1.760200000000001</v>
       </c>
       <c r="L13" t="n">
-        <v>3.911699999999999</v>
+        <v>3.9117</v>
       </c>
       <c r="M13" t="n">
         <v>-30.2125</v>
@@ -1468,13 +1468,13 @@
         <v>19.5848</v>
       </c>
       <c r="S13" t="n">
-        <v>2.9937</v>
+        <v>3.2906</v>
       </c>
       <c r="T13" t="n">
-        <v>1.4115</v>
+        <v>1.7086</v>
       </c>
       <c r="U13" t="n">
-        <v>1.5821</v>
+        <v>1.5823</v>
       </c>
       <c r="V13" t="n">
         <v>1.4919</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>10.3895</v>
+        <v>11.5096</v>
       </c>
       <c r="E14" t="n">
-        <v>9.0045</v>
+        <v>9.311500000000001</v>
       </c>
       <c r="F14" t="n">
-        <v>1.3849</v>
+        <v>2.198</v>
       </c>
       <c r="G14" t="n">
         <v>8.123100000000001</v>
@@ -1546,13 +1546,13 @@
         <v>1.9585</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.5009</v>
+        <v>-0.3808</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.4223</v>
+        <v>-0.1153</v>
       </c>
       <c r="U14" t="n">
-        <v>-1.0786</v>
+        <v>-0.2655</v>
       </c>
       <c r="V14" t="n">
         <v>2.9839</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>7.617</v>
+        <v>7.2835</v>
       </c>
       <c r="E15" t="n">
-        <v>2.4249</v>
+        <v>2.8342</v>
       </c>
       <c r="F15" t="n">
-        <v>5.1921</v>
+        <v>4.4493</v>
       </c>
       <c r="G15" t="n">
         <v>7.8101</v>
@@ -1624,13 +1624,13 @@
         <v>2.7419</v>
       </c>
       <c r="S15" t="n">
-        <v>0.8449</v>
+        <v>0.5114</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.6246</v>
+        <v>-0.2153</v>
       </c>
       <c r="U15" t="n">
-        <v>1.4695</v>
+        <v>0.7267</v>
       </c>
       <c r="V15" t="n">
         <v>0.3329</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>5.9699</v>
+        <v>6.8189</v>
       </c>
       <c r="E16" t="n">
-        <v>6.2256</v>
+        <v>6.021</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.2557</v>
+        <v>0.798</v>
       </c>
       <c r="G16" t="n">
         <v>6.6523</v>
@@ -1702,13 +1702,13 @@
         <v>2.7419</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.27</v>
+        <v>-0.421</v>
       </c>
       <c r="T16" t="n">
-        <v>0.1411</v>
+        <v>-0.0635</v>
       </c>
       <c r="U16" t="n">
-        <v>-1.4111</v>
+        <v>-0.3574</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>4.5552</v>
+        <v>4.5138</v>
       </c>
       <c r="E17" t="n">
-        <v>2.8548</v>
+        <v>2.2408</v>
       </c>
       <c r="F17" t="n">
-        <v>1.7004</v>
+        <v>2.2729</v>
       </c>
       <c r="G17" t="n">
         <v>3.7918</v>
@@ -1780,13 +1780,13 @@
         <v>2.3502</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.1363</v>
+        <v>-0.1778</v>
       </c>
       <c r="T17" t="n">
-        <v>0.6693</v>
+        <v>0.0553</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.8056</v>
+        <v>-0.233</v>
       </c>
       <c r="V17" t="n">
         <v>-0.2754</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.9942</v>
+        <v>1.6383</v>
       </c>
       <c r="E18" t="n">
-        <v>1.4868</v>
+        <v>1.0774</v>
       </c>
       <c r="F18" t="n">
-        <v>0.5074</v>
+        <v>0.5608</v>
       </c>
       <c r="G18" t="n">
         <v>0.8279</v>
@@ -1858,13 +1858,13 @@
         <v>0.5875</v>
       </c>
       <c r="S18" t="n">
-        <v>0.6167</v>
+        <v>0.2608</v>
       </c>
       <c r="T18" t="n">
-        <v>0.3611</v>
+        <v>-0.0482</v>
       </c>
       <c r="U18" t="n">
-        <v>0.2556</v>
+        <v>0.3091</v>
       </c>
       <c r="V18" t="n">
         <v>0.9412</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. FERNÁNDEZ DEL RÍO</t>
+          <t>M. SAN MILLAN GONZALEZ-QUEVEDO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,58 +1891,58 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.3361</v>
+        <v>-0.3703</v>
       </c>
       <c r="E19" t="n">
-        <v>0.5683</v>
+        <v>-0.724</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.9043</v>
+        <v>0.3537</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.4608</v>
+        <v>-0.6135</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.3396</v>
+        <v>-0.6135</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.1212</v>
+        <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>0.6871</v>
+        <v>-0.6822</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>-0.6822</v>
       </c>
       <c r="L19" t="n">
-        <v>0.6871</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.1479</v>
+        <v>0.0687</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.3396</v>
+        <v>0.0687</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.8083</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>0.1958</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>0.1958</v>
       </c>
       <c r="S19" t="n">
-        <v>0.1247</v>
+        <v>0.0473</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.1188</v>
+        <v>-0.0418</v>
       </c>
       <c r="U19" t="n">
-        <v>0.2435</v>
+        <v>0.0891</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>M. SAN MILLAN GONZALEZ-QUEVEDO</t>
+          <t>J. FERNÁNDEZ DEL RÍO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,58 +1969,58 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.4238</v>
+        <v>-0.4163</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.724</v>
+        <v>0.5683</v>
       </c>
       <c r="F20" t="n">
-        <v>0.3002</v>
+        <v>-0.9845</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.6135</v>
+        <v>-0.4608</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.6135</v>
+        <v>-0.3396</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>-0.1212</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.6822</v>
+        <v>0.6871</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.6822</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>0.6871</v>
       </c>
       <c r="M20" t="n">
-        <v>0.0687</v>
+        <v>-1.1479</v>
       </c>
       <c r="N20" t="n">
-        <v>0.0687</v>
+        <v>-0.3396</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>-0.8083</v>
       </c>
       <c r="P20" t="n">
-        <v>0.1958</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.1958</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.0061</v>
+        <v>0.0446</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.0418</v>
+        <v>-0.1188</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0356</v>
+        <v>0.1634</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.7403999999999999</v>
+        <v>-0.4545</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.5642</v>
+        <v>-0.2572</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.1762</v>
+        <v>-0.1974</v>
       </c>
       <c r="G21" t="n">
         <v>2.9675</v>
@@ -2092,13 +2092,13 @@
         <v>1.9585</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.09959999999999999</v>
+        <v>0.1863</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.5652</v>
+        <v>-0.2582</v>
       </c>
       <c r="U21" t="n">
-        <v>0.4656</v>
+        <v>0.4445</v>
       </c>
       <c r="V21" t="n">
         <v>-2.4332</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.1814</v>
+        <v>-2.5389</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.5812</v>
+        <v>-3.4788</v>
       </c>
       <c r="F22" t="n">
-        <v>0.3997</v>
+        <v>0.9399</v>
       </c>
       <c r="G22" t="n">
         <v>-0.1023</v>
@@ -2170,13 +2170,13 @@
         <v>2.1543</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.7658</v>
+        <v>-0.1232</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.4223</v>
+        <v>-0.3199</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.3435</v>
+        <v>0.1967</v>
       </c>
       <c r="V22" t="n">
         <v>-0.5507</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.2064</v>
+        <v>-4.6173</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.6234</v>
+        <v>-3.5211</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.583</v>
+        <v>-1.0962</v>
       </c>
       <c r="G23" t="n">
         <v>-0.9350000000000001</v>
@@ -2248,13 +2248,13 @@
         <v>1.9585</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.8014</v>
+        <v>-0.2123</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.5587</v>
+        <v>-0.4564</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.2427</v>
+        <v>0.2441</v>
       </c>
       <c r="V23" t="n">
         <v>-2.4908</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>20.6377</v>
+        <v>23.3668</v>
       </c>
       <c r="E24" t="n">
         <v>14.0721</v>
       </c>
       <c r="F24" t="n">
-        <v>6.565499999999998</v>
+        <v>9.294499999999999</v>
       </c>
       <c r="G24" t="n">
         <v>28.0611</v>
@@ -2326,13 +2326,13 @@
         <v>16.6471</v>
       </c>
       <c r="S24" t="n">
-        <v>-2.9938</v>
+        <v>-0.2647000000000002</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.5822</v>
+        <v>-1.5821</v>
       </c>
       <c r="U24" t="n">
-        <v>-1.4117</v>
+        <v>1.3177</v>
       </c>
       <c r="V24" t="n">
         <v>-1.4921</v>
